--- a/AFTER onedrive is back/AFTER cutover/OEM_jobs_reference.xlsx
+++ b/AFTER onedrive is back/AFTER cutover/OEM_jobs_reference.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rods/Documents/GitHub/tenarai/AFTER onedrive is back/AFTER cutover/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C24F6F69-24AE-F440-ADC1-4554528FC2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B03B855-9050-C64A-9BDA-3DECD7DB1145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-12020" yWindow="-21600" windowWidth="51200" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OEM Jobs" sheetId="1" r:id="rId1"/>
@@ -1831,6 +1831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:N129"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1893,7 +1894,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
         <v>14</v>
       </c>
@@ -1911,7 +1912,7 @@
       <c r="M2" s="17"/>
       <c r="N2" s="17"/>
     </row>
-    <row r="3" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1951,7 +1952,7 @@
       </c>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -1989,7 +1990,7 @@
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
     </row>
-    <row r="5" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
@@ -2029,7 +2030,7 @@
       </c>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -2069,7 +2070,7 @@
       </c>
       <c r="N6" s="2"/>
     </row>
-    <row r="7" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -2109,7 +2110,7 @@
       </c>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -2149,7 +2150,7 @@
       </c>
       <c r="N8" s="2"/>
     </row>
-    <row r="9" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -2189,7 +2190,7 @@
       </c>
       <c r="N9" s="2"/>
     </row>
-    <row r="10" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>15</v>
       </c>
@@ -2229,7 +2230,7 @@
       </c>
       <c r="N10" s="8"/>
     </row>
-    <row r="11" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>15</v>
       </c>
@@ -2269,7 +2270,7 @@
       </c>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>15</v>
       </c>
@@ -2309,7 +2310,7 @@
       </c>
       <c r="N12" s="8"/>
     </row>
-    <row r="13" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -2349,7 +2350,7 @@
       </c>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>15</v>
       </c>
@@ -2389,7 +2390,7 @@
       </c>
       <c r="N14" s="8"/>
     </row>
-    <row r="15" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
@@ -2429,7 +2430,7 @@
       </c>
       <c r="N15" s="2"/>
     </row>
-    <row r="16" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>15</v>
       </c>
@@ -2469,7 +2470,7 @@
       </c>
       <c r="N16" s="8"/>
     </row>
-    <row r="17" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
@@ -2549,7 +2550,7 @@
       </c>
       <c r="N18" s="6"/>
     </row>
-    <row r="19" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>15</v>
       </c>
@@ -2589,7 +2590,7 @@
       </c>
       <c r="N19" s="8"/>
     </row>
-    <row r="20" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>15</v>
       </c>
@@ -2629,7 +2630,7 @@
       </c>
       <c r="N20" s="8"/>
     </row>
-    <row r="21" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>15</v>
       </c>
@@ -2669,7 +2670,7 @@
       </c>
       <c r="N21" s="8"/>
     </row>
-    <row r="22" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>15</v>
       </c>
@@ -2709,7 +2710,7 @@
       </c>
       <c r="N22" s="2"/>
     </row>
-    <row r="23" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>15</v>
       </c>
@@ -2749,7 +2750,7 @@
       </c>
       <c r="N23" s="2"/>
     </row>
-    <row r="24" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>15</v>
       </c>
@@ -2789,7 +2790,7 @@
       </c>
       <c r="N24" s="2"/>
     </row>
-    <row r="25" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>15</v>
       </c>
@@ -2829,7 +2830,7 @@
       </c>
       <c r="N25" s="2"/>
     </row>
-    <row r="26" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>15</v>
       </c>
@@ -2869,7 +2870,7 @@
       </c>
       <c r="N26" s="2"/>
     </row>
-    <row r="27" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>15</v>
       </c>
@@ -2909,7 +2910,7 @@
       </c>
       <c r="N27" s="2"/>
     </row>
-    <row r="28" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>15</v>
       </c>
@@ -2947,7 +2948,7 @@
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
     </row>
-    <row r="29" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>15</v>
       </c>
@@ -2987,7 +2988,7 @@
       </c>
       <c r="N29" s="8"/>
     </row>
-    <row r="30" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>15</v>
       </c>
@@ -3027,7 +3028,7 @@
       </c>
       <c r="N30" s="6"/>
     </row>
-    <row r="31" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
@@ -3065,7 +3066,7 @@
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
     </row>
-    <row r="32" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>15</v>
       </c>
@@ -3105,7 +3106,7 @@
       </c>
       <c r="N32" s="8"/>
     </row>
-    <row r="33" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>15</v>
       </c>
@@ -3145,7 +3146,7 @@
       </c>
       <c r="N33" s="6"/>
     </row>
-    <row r="34" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>15</v>
       </c>
@@ -3185,7 +3186,7 @@
       </c>
       <c r="N34" s="2"/>
     </row>
-    <row r="35" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="16" t="s">
         <v>162</v>
       </c>
@@ -3203,7 +3204,7 @@
       <c r="M35" s="17"/>
       <c r="N35" s="17"/>
     </row>
-    <row r="36" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>15</v>
       </c>
@@ -3243,7 +3244,7 @@
       </c>
       <c r="N36" s="2"/>
     </row>
-    <row r="37" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="16" t="s">
         <v>14</v>
       </c>
@@ -3261,7 +3262,7 @@
       <c r="M37" s="17"/>
       <c r="N37" s="17"/>
     </row>
-    <row r="38" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
         <v>15</v>
       </c>
@@ -3301,7 +3302,7 @@
       </c>
       <c r="N38" s="6"/>
     </row>
-    <row r="39" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>15</v>
       </c>
@@ -3341,7 +3342,7 @@
       </c>
       <c r="N39" s="2"/>
     </row>
-    <row r="40" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
         <v>174</v>
       </c>
@@ -3383,7 +3384,7 @@
       </c>
       <c r="N40" s="10"/>
     </row>
-    <row r="41" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>179</v>
       </c>
@@ -3425,7 +3426,7 @@
       </c>
       <c r="N41" s="12"/>
     </row>
-    <row r="42" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>15</v>
       </c>
@@ -3465,7 +3466,7 @@
       </c>
       <c r="N42" s="2"/>
     </row>
-    <row r="43" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>15</v>
       </c>
@@ -3505,7 +3506,7 @@
       </c>
       <c r="N43" s="2"/>
     </row>
-    <row r="44" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="s">
         <v>174</v>
       </c>
@@ -3547,7 +3548,7 @@
       </c>
       <c r="N44" s="10"/>
     </row>
-    <row r="45" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>179</v>
       </c>
@@ -3589,7 +3590,7 @@
       </c>
       <c r="N45" s="12"/>
     </row>
-    <row r="46" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>15</v>
       </c>
@@ -3629,7 +3630,7 @@
       </c>
       <c r="N46" s="2"/>
     </row>
-    <row r="47" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
         <v>174</v>
       </c>
@@ -3671,7 +3672,7 @@
       </c>
       <c r="N47" s="10"/>
     </row>
-    <row r="48" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>179</v>
       </c>
@@ -3713,7 +3714,7 @@
       </c>
       <c r="N48" s="12"/>
     </row>
-    <row r="49" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>15</v>
       </c>
@@ -3753,7 +3754,7 @@
       </c>
       <c r="N49" s="2"/>
     </row>
-    <row r="50" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>15</v>
       </c>
@@ -3793,7 +3794,7 @@
       </c>
       <c r="N50" s="2"/>
     </row>
-    <row r="51" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>15</v>
       </c>
@@ -3833,7 +3834,7 @@
       </c>
       <c r="N51" s="8"/>
     </row>
-    <row r="52" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>15</v>
       </c>
@@ -3873,7 +3874,7 @@
       </c>
       <c r="N52" s="2"/>
     </row>
-    <row r="53" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>15</v>
       </c>
@@ -3913,7 +3914,7 @@
       </c>
       <c r="N53" s="2"/>
     </row>
-    <row r="54" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="16" t="s">
         <v>162</v>
       </c>
@@ -3931,7 +3932,7 @@
       <c r="M54" s="17"/>
       <c r="N54" s="17"/>
     </row>
-    <row r="55" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>15</v>
       </c>
@@ -3971,7 +3972,7 @@
       </c>
       <c r="N55" s="2"/>
     </row>
-    <row r="56" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>15</v>
       </c>
@@ -4011,7 +4012,7 @@
       </c>
       <c r="N56" s="2"/>
     </row>
-    <row r="57" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>15</v>
       </c>
@@ -4051,7 +4052,7 @@
       </c>
       <c r="N57" s="2"/>
     </row>
-    <row r="58" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>15</v>
       </c>
@@ -4091,7 +4092,7 @@
       </c>
       <c r="N58" s="8"/>
     </row>
-    <row r="59" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>15</v>
       </c>
@@ -4131,7 +4132,7 @@
       </c>
       <c r="N59" s="8"/>
     </row>
-    <row r="60" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>15</v>
       </c>
@@ -4171,7 +4172,7 @@
       </c>
       <c r="N60" s="4"/>
     </row>
-    <row r="61" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="8" t="s">
         <v>15</v>
       </c>
@@ -4211,7 +4212,7 @@
       </c>
       <c r="N61" s="8"/>
     </row>
-    <row r="62" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="10" t="s">
         <v>174</v>
       </c>
@@ -4253,7 +4254,7 @@
       </c>
       <c r="N62" s="10"/>
     </row>
-    <row r="63" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>15</v>
       </c>
@@ -4291,7 +4292,7 @@
       <c r="M63" s="4"/>
       <c r="N63" s="4"/>
     </row>
-    <row r="64" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>15</v>
       </c>
@@ -4331,7 +4332,7 @@
       </c>
       <c r="N64" s="2"/>
     </row>
-    <row r="65" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>15</v>
       </c>
@@ -4371,7 +4372,7 @@
       </c>
       <c r="N65" s="2"/>
     </row>
-    <row r="66" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
         <v>15</v>
       </c>
@@ -4451,7 +4452,7 @@
       </c>
       <c r="N67" s="8"/>
     </row>
-    <row r="68" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
         <v>15</v>
       </c>
@@ -4491,7 +4492,7 @@
       </c>
       <c r="N68" s="8"/>
     </row>
-    <row r="69" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>15</v>
       </c>
@@ -4531,7 +4532,7 @@
       </c>
       <c r="N69" s="2"/>
     </row>
-    <row r="70" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
         <v>15</v>
       </c>
@@ -4571,7 +4572,7 @@
       </c>
       <c r="N70" s="8"/>
     </row>
-    <row r="71" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>15</v>
       </c>
@@ -4611,7 +4612,7 @@
       </c>
       <c r="N71" s="2"/>
     </row>
-    <row r="72" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>15</v>
       </c>
@@ -4651,7 +4652,7 @@
       </c>
       <c r="N72" s="2"/>
     </row>
-    <row r="73" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>15</v>
       </c>
@@ -4691,7 +4692,7 @@
       </c>
       <c r="N73" s="2"/>
     </row>
-    <row r="74" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>15</v>
       </c>
@@ -4729,7 +4730,7 @@
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
     </row>
-    <row r="75" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>15</v>
       </c>
@@ -4769,7 +4770,7 @@
       </c>
       <c r="N75" s="2"/>
     </row>
-    <row r="76" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
         <v>15</v>
       </c>
@@ -4809,7 +4810,7 @@
       </c>
       <c r="N76" s="6"/>
     </row>
-    <row r="77" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>15</v>
       </c>
@@ -4847,7 +4848,7 @@
       <c r="M77" s="4"/>
       <c r="N77" s="4"/>
     </row>
-    <row r="78" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
         <v>15</v>
       </c>
@@ -4887,7 +4888,7 @@
       </c>
       <c r="N78" s="8"/>
     </row>
-    <row r="79" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="s">
         <v>15</v>
       </c>
@@ -4927,7 +4928,7 @@
       </c>
       <c r="N79" s="6"/>
     </row>
-    <row r="80" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>15</v>
       </c>
@@ -4967,7 +4968,7 @@
       </c>
       <c r="N80" s="2"/>
     </row>
-    <row r="81" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>15</v>
       </c>
@@ -5005,7 +5006,7 @@
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
     </row>
-    <row r="82" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>15</v>
       </c>
@@ -5045,7 +5046,7 @@
       </c>
       <c r="N82" s="2"/>
     </row>
-    <row r="83" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>15</v>
       </c>
@@ -5085,7 +5086,7 @@
       </c>
       <c r="N83" s="2"/>
     </row>
-    <row r="84" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>15</v>
       </c>
@@ -5123,7 +5124,7 @@
       <c r="M84" s="4"/>
       <c r="N84" s="4"/>
     </row>
-    <row r="85" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>15</v>
       </c>
@@ -5163,7 +5164,7 @@
       </c>
       <c r="N85" s="8"/>
     </row>
-    <row r="86" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>15</v>
       </c>
@@ -5201,7 +5202,7 @@
       <c r="M86" s="4"/>
       <c r="N86" s="4"/>
     </row>
-    <row r="87" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>15</v>
       </c>
@@ -5241,7 +5242,7 @@
       </c>
       <c r="N87" s="2"/>
     </row>
-    <row r="88" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6" t="s">
         <v>15</v>
       </c>
@@ -5281,7 +5282,7 @@
       </c>
       <c r="N88" s="6"/>
     </row>
-    <row r="89" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>15</v>
       </c>
@@ -5321,7 +5322,7 @@
       </c>
       <c r="N89" s="8"/>
     </row>
-    <row r="90" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>15</v>
       </c>
@@ -5361,7 +5362,7 @@
       </c>
       <c r="N90" s="2"/>
     </row>
-    <row r="91" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>15</v>
       </c>
@@ -5401,7 +5402,7 @@
       </c>
       <c r="N91" s="2"/>
     </row>
-    <row r="92" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>15</v>
       </c>
@@ -5441,7 +5442,7 @@
       </c>
       <c r="N92" s="2"/>
     </row>
-    <row r="93" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>15</v>
       </c>
@@ -5481,7 +5482,7 @@
       </c>
       <c r="N93" s="2"/>
     </row>
-    <row r="94" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>15</v>
       </c>
@@ -5521,7 +5522,7 @@
       </c>
       <c r="N94" s="2"/>
     </row>
-    <row r="95" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:14" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="16" t="s">
         <v>14</v>
       </c>
@@ -5539,7 +5540,7 @@
       <c r="M95" s="17"/>
       <c r="N95" s="17"/>
     </row>
-    <row r="96" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="10" t="s">
         <v>174</v>
       </c>
@@ -5579,7 +5580,7 @@
       <c r="M96" s="10"/>
       <c r="N96" s="10"/>
     </row>
-    <row r="97" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="16" t="s">
         <v>162</v>
       </c>
@@ -5597,7 +5598,7 @@
       <c r="M97" s="17"/>
       <c r="N97" s="17"/>
     </row>
-    <row r="98" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="10" t="s">
         <v>174</v>
       </c>
@@ -5637,7 +5638,7 @@
       <c r="M98" s="10"/>
       <c r="N98" s="10"/>
     </row>
-    <row r="99" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="16" t="s">
         <v>14</v>
       </c>
@@ -5655,7 +5656,7 @@
       <c r="M99" s="17"/>
       <c r="N99" s="17"/>
     </row>
-    <row r="100" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="10" t="s">
         <v>174</v>
       </c>
@@ -5697,7 +5698,7 @@
       </c>
       <c r="N100" s="10"/>
     </row>
-    <row r="101" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="8" t="s">
         <v>15</v>
       </c>
@@ -5737,7 +5738,7 @@
       </c>
       <c r="N101" s="8"/>
     </row>
-    <row r="102" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="16" t="s">
         <v>162</v>
       </c>
@@ -5755,7 +5756,7 @@
       <c r="M102" s="17"/>
       <c r="N102" s="17"/>
     </row>
-    <row r="103" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>15</v>
       </c>
@@ -5793,7 +5794,7 @@
       <c r="M103" s="4"/>
       <c r="N103" s="4"/>
     </row>
-    <row r="104" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:14" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="16" t="s">
         <v>14</v>
       </c>
@@ -5811,7 +5812,7 @@
       <c r="M104" s="17"/>
       <c r="N104" s="17"/>
     </row>
-    <row r="105" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="10" t="s">
         <v>174</v>
       </c>
@@ -5853,7 +5854,7 @@
       </c>
       <c r="N105" s="10"/>
     </row>
-    <row r="106" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="12" t="s">
         <v>179</v>
       </c>
@@ -5895,7 +5896,7 @@
       </c>
       <c r="N106" s="12"/>
     </row>
-    <row r="107" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>15</v>
       </c>
@@ -5935,7 +5936,7 @@
       </c>
       <c r="N107" s="2"/>
     </row>
-    <row r="108" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="10" t="s">
         <v>174</v>
       </c>
@@ -5977,7 +5978,7 @@
       </c>
       <c r="N108" s="10"/>
     </row>
-    <row r="109" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
         <v>15</v>
       </c>
@@ -6017,7 +6018,7 @@
       </c>
       <c r="N109" s="2"/>
     </row>
-    <row r="110" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="10" t="s">
         <v>174</v>
       </c>
@@ -6059,7 +6060,7 @@
       </c>
       <c r="N110" s="10"/>
     </row>
-    <row r="111" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="10" t="s">
         <v>174</v>
       </c>
@@ -6101,7 +6102,7 @@
       </c>
       <c r="N111" s="10"/>
     </row>
-    <row r="112" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="8" t="s">
         <v>15</v>
       </c>
@@ -6141,7 +6142,7 @@
       </c>
       <c r="N112" s="8"/>
     </row>
-    <row r="113" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:14" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="16" t="s">
         <v>162</v>
       </c>
@@ -6159,7 +6160,7 @@
       <c r="M113" s="17"/>
       <c r="N113" s="17"/>
     </row>
-    <row r="114" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
         <v>15</v>
       </c>
@@ -6199,7 +6200,7 @@
       </c>
       <c r="N114" s="8"/>
     </row>
-    <row r="115" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:14" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="16" t="s">
         <v>14</v>
       </c>
@@ -6217,7 +6218,7 @@
       <c r="M115" s="17"/>
       <c r="N115" s="17"/>
     </row>
-    <row r="116" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="10" t="s">
         <v>174</v>
       </c>
@@ -6257,7 +6258,7 @@
       <c r="M116" s="10"/>
       <c r="N116" s="10"/>
     </row>
-    <row r="117" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="12" t="s">
         <v>179</v>
       </c>
@@ -6299,7 +6300,7 @@
       </c>
       <c r="N117" s="12"/>
     </row>
-    <row r="118" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>15</v>
       </c>
@@ -6339,7 +6340,7 @@
       </c>
       <c r="N118" s="2"/>
     </row>
-    <row r="119" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:14" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="16" t="s">
         <v>162</v>
       </c>
@@ -6357,7 +6358,7 @@
       <c r="M119" s="17"/>
       <c r="N119" s="17"/>
     </row>
-    <row r="120" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>15</v>
       </c>
@@ -6397,7 +6398,7 @@
       </c>
       <c r="N120" s="2"/>
     </row>
-    <row r="121" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:14" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="12" t="s">
         <v>179</v>
       </c>
@@ -6578,7 +6579,13 @@
       <c r="N129" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N121" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:N121" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="MAZ"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="13">
     <mergeCell ref="A123:N123"/>
     <mergeCell ref="A35:N35"/>
